--- a/artfynd/A 19870-2026 artfynd.xlsx
+++ b/artfynd/A 19870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,6 +1339,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132914447</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>423102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6802942</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19870-2026 artfynd.xlsx
+++ b/artfynd/A 19870-2026 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>132914447</v>
       </c>
       <c r="B8" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19870-2026 artfynd.xlsx
+++ b/artfynd/A 19870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150102</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132914447</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150106</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150104</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,8 +1445,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150103</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>